--- a/docs/sample_risk_register.xlsx
+++ b/docs/sample_risk_register.xlsx
@@ -1613,7 +1613,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes. Customers receive at least 30 days notice before any material change to the underlying models used for summarization, including a change of model provider.</t>
+          <t>Customers receive at least 30 days notice before any material change to the underlying models used for summarization, including a change of model provider.</t>
         </is>
       </c>
     </row>

--- a/docs/sample_risk_register.xlsx
+++ b/docs/sample_risk_register.xlsx
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meeting transcripts and derived summaries are retained for the life of the account and are not subject to a fixed deletion schedule. We retain this content indefinitely to support product improvement and historical search functionality.</t>
+          <t>Meeting transcripts and derived summaries are retained for the life of the account and are not subject to a fixed deletion schedule.</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No. Once an integration is authorized, the assistant posts summaries and creates tasks automatically without per-action confirmation.</t>
+          <t>Once an integration is authorized, the assistant posts summaries and creates tasks automatically without per-action confirmation.</t>
         </is>
       </c>
     </row>

--- a/docs/sample_risk_register.xlsx
+++ b/docs/sample_risk_register.xlsx
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Once an integration is authorized, the assistant posts summaries and creates tasks automatically without per-action confirmation.</t>
+          <t>No. Once an integration is authorized, the assistant posts summaries and creates tasks automatically without per-action confirmation.</t>
         </is>
       </c>
     </row>
